--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_preview.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_preview.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
   <si>
     <t>编号</t>
   </si>
@@ -135,7 +135,7 @@
     <t>开启时间#全天开启&amp;游戏玩法#1.消耗1[透明披风]，根据自身等级，选择进入的层数。帮助受伤的大天使获取大天使之剑，即可获得奖励。\n2.在副本内击杀怪物有大量经验可以获得。\n3.每天限制次数4次，限制次数共享恶魔广场。</t>
   </si>
   <si>
-    <t>10010002#1000</t>
+    <t>10010002#10000</t>
   </si>
   <si>
     <t>dev/outui/Activity/Panel/KLActivityDetail/KLActivityDetailPanel#11001</t>
@@ -162,7 +162,7 @@
     <t>游戏攻略</t>
   </si>
   <si>
-    <t>版本介绍：1.03H版本！5/6/7点 一切靠打，经典设置！&amp;线路规划：和平线路（不可PK）；PK线路（杀人不加杀气）&amp;装备设置：强化最高+15，全身强7以上额外增加强化大师属性，追加最高16，另外卓越最高6词条&amp;技能设置：战士-生命之光最高30%，法师-守护之魂最高30%，弓手BUFF最高120点攻击和120点防御&amp;回收设置：装备回收得金币，卓越装备/宝石/马魂/羽毛/套装/卓越套装/回收得积分，&amp;回收设置：宝石/白装/幸运装/强化装/支持自动回收，贵重物品手动回收。仔细阅读回收面板</t>
+    <t>版本介绍：雷霆纪元1.03H版本！ 一切靠打！&amp;装备设置：强化最高+15，全身强7以上额外增加强化大师属性，追加最高16，卓越最高6词条&amp;回收设置：装备回收得金币，卓越装备/宝石/马魂/羽毛/套装/卓越套装/回收得积分，&amp;回收设置：宝石/白装/幸运装/强化装/支持自动回收，贵重物品手动回收。仔细阅读回收面板</t>
   </si>
   <si>
     <t>Atlas/KmlPreviewUI.spriteatlas#icon_langhunyaosai</t>
@@ -171,7 +171,7 @@
     <t>狼魂要塞</t>
   </si>
   <si>
-    <t>开启时间#每周一晚上8点30分&amp;游戏玩法#1.所有拥有战盟的玩家都可进入副本进行战斗。\n2.盟主及副盟主可消耗战盟资金召唤守护者共同战斗。\n3.战斗开始时，会在副本随机刷新出怪物朝狼神护台进攻，玩家需要将怪物在击败狼神护台前进行击杀。\n4.成功守护狼神护台后，获得奖励</t>
+    <t>开启时间#每周一/四/日晚上8点30分&amp;游戏玩法#1.所有拥有战盟的玩家都可进入副本进行战斗。\n2.盟主及副盟主可消耗战盟资金召唤守护者共同战斗。\n3.战斗开始时，会在副本随机刷新出怪物朝狼神护台进攻，玩家需要将怪物在击败狼神护台前进行击杀&amp;狼魂要塞产出：稀有装备，终极套装（非终级洞装）坐骑材料。&amp;狼魂要塞为行会战盟副本/增加BOSS阶段</t>
   </si>
   <si>
     <t>强化大师</t>
@@ -186,10 +186,10 @@
     <t>宝石掉落：小怪和BOSS均可掉落宝石&amp;冰风谷-Lv.20：祝福宝石。&amp;地下城-Lv.30：祝福宝石、灵魂宝石。&amp;失落之塔-Lv.40：祝福宝石、灵魂宝石、玛雅之石。&amp;亚特兰蒂斯-Lv.70：祝福宝石、灵魂宝石、玛雅之石、生命宝石。&amp;死亡沙漠以上-Lv.130：祝福宝石、灵魂宝石、玛雅之石、生命宝石、创造宝石。</t>
   </si>
   <si>
-    <t>自由交易</t>
-  </si>
-  <si>
-    <t>开通畅玩卡：玩家自由交易需双方均畅玩卡。&amp;建议玩家前往勇者大陆交易专线进行交易。&amp;交易限制：交易双方必须在本服、非副本、同地图内，不超过3格距离，建议选择安全区。&amp;交易税：交易货币存在10%交易税。&amp;交易失败：离线、死亡等异常状况会导致交易失败。 &amp;交易过程中，任何一方关闭界面，交易停止</t>
+    <t>交易系统</t>
+  </si>
+  <si>
+    <t>开通畅玩卡：玩家自由交易需双方均畅玩卡。&amp;交易限制：交易双方必须在本服、非副本、同地图内，不超过4格距离，建议选择安全区。&amp;交易税：交易货币存在9%交易税。&amp;交易失败：离线、死亡等异常状况会导致交易失败。 &amp;交易过程中，任何一方关闭界面，交易取消</t>
   </si>
   <si>
     <t>红名PK系统</t>
@@ -201,13 +201,31 @@
     <t>萤石系统</t>
   </si>
   <si>
-    <t>萤石玩法详解：幻术园：47 242 可用套装抽取荧之石&amp; 荧之石加光之石可合成荧光宝石&amp; 相同的荧光宝石（属性可不一样）且相同级别的荧光宝石+光之石强化符文可合成高等级荧光宝石</t>
+    <t>萤石玩法详解：#幻术园：47 242 可用套装抽取荧之石：\n荧之石加光之石可合成荧光宝石\n相同的荧光宝石（属性可不一样）且相同级别的荧光宝石+光之石强化符文可合成高等级荧光宝石\n光之石，在安宁池产出，光之石强化符文冰霜地图后面BOSS产出</t>
   </si>
   <si>
     <t>耳环系统</t>
   </si>
   <si>
-    <t>耳环获取详解：幻术园：23 226 可用灵魂/祝福/玛雅/各一个合成饰品箱子&amp; 可以开出卓越装备/套装/耳环&amp;耳环唯一产出的地方</t>
+    <t>耳环获取详解：#幻术园：23 226 可用灵魂/祝福/玛雅/各一个合成饰品箱子\n可以开出卓越装备/套装/耳环/技能书/耳环/积分/金币/一切看脸。搏一搏单车变摩托。一切皆有可能。 &amp;宝箱系统永远免费合成/全部玩家游戏打材料产出</t>
+  </si>
+  <si>
+    <t>挂机玩法</t>
+  </si>
+  <si>
+    <t>挂机点说明：#每条线路/每张大地图/有一个怪物点，。需玩家自行探索&amp;高等级地图会有2-3个</t>
+  </si>
+  <si>
+    <t>合成系统</t>
+  </si>
+  <si>
+    <t>坐骑合成：#越高等级坐骑出现卓越词条几率越大&amp;满卓越6词条&amp;高等级坐骑增加移动速度&amp;在PVP,PVE中更有优势&amp;翅膀合成：#合成逻辑严格按照1.03H版本支持拔毛\n合成成功率所溢出的材料将会退回到背包不计算在内，保证玩家的材料避免丢失</t>
+  </si>
+  <si>
+    <t>重要提示</t>
+  </si>
+  <si>
+    <t>AG/SD详解：#战斗数值复原1.03.Ag值，各职业增加对应的属性点，会有对应的AG/SD值加成。\n具体数值需玩家自行摸索。\nSD值，除基础属性提升，属性加成提升，高等级装备也会增加SD值。&amp;重要货币提醒：所有货币均为单角色储存，同账号多职业/角色不通用。</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1395,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1566,7 +1584,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" ht="57" spans="1:9">
+    <row r="7" ht="42.75" spans="1:9">
       <c r="A7" s="3">
         <v>9</v>
       </c>
@@ -1634,10 +1652,10 @@
         <v>48</v>
       </c>
       <c r="E9" s="3">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="F9" s="3">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="G9" s="3">
         <v>9999</v>
@@ -1754,7 +1772,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" ht="28.5" spans="1:9">
       <c r="A14" s="1">
         <v>17</v>
       </c>
@@ -1781,7 +1799,82 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="B15" s="3"/>
+      <c r="A15" s="1">
+        <v>18</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>9999</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" ht="28.5" spans="1:9">
+      <c r="A16" s="1">
+        <v>19</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>9999</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" ht="42.75" spans="1:8">
+      <c r="A17" s="1">
+        <v>21</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>9999</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_preview.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_preview.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_preview" sheetId="1" r:id="rId1"/>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_preview.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_preview.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_preview" sheetId="1" r:id="rId1"/>
@@ -162,7 +167,13 @@
     <t>游戏攻略</t>
   </si>
   <si>
-    <t>版本介绍：雷霆纪元1.03H版本！ 一切靠打！&amp;装备设置：强化最高+15，全身强7以上额外增加强化大师属性，追加最高16，卓越最高6词条&amp;回收设置：装备回收得金币，卓越装备/宝石/马魂/羽毛/套装/卓越套装/回收得积分，&amp;回收设置：宝石/白装/幸运装/强化装/支持自动回收，贵重物品手动回收。仔细阅读回收面板</t>
+    <t>版本介绍：所有人统一起跑线 一切靠打！&amp;装备设置：强化最高+15，全身强7以上额外增加强化大师属性，追加最高16，卓越最高6词条&amp;回收设置：装备回收得金币，卓越装备/宝石/羽毛/套装/卓越套装/回收得积分，&amp;回收设置：宝石/白装/幸运装/强化装/支持自动回收，贵重物品手动回收。仔细阅读回收面板/积分只能在游戏里面打怪回收装备获取。</t>
+  </si>
+  <si>
+    <t>游戏玩法设定</t>
+  </si>
+  <si>
+    <t>版本介绍：#1.无任何游戏数值道具氪点\n2.无自由交易系统，藏宝阁系统只要开通（畅玩卡）可以自由使用藏宝阁。\n3.本游戏没有特殊设置。\n4.全部免费，只要用时间去打一切皆有可能\n5.所有玩家统一起跑线/所有玩家氪点一样</t>
   </si>
   <si>
     <t>Atlas/KmlPreviewUI.spriteatlas#icon_langhunyaosai</t>
@@ -171,13 +182,7 @@
     <t>狼魂要塞</t>
   </si>
   <si>
-    <t>开启时间#每周一/四/日晚上8点30分&amp;游戏玩法#1.所有拥有战盟的玩家都可进入副本进行战斗。\n2.盟主及副盟主可消耗战盟资金召唤守护者共同战斗。\n3.战斗开始时，会在副本随机刷新出怪物朝狼神护台进攻，玩家需要将怪物在击败狼神护台前进行击杀&amp;狼魂要塞产出：稀有装备，终极套装（非终级洞装）坐骑材料。&amp;狼魂要塞为行会战盟副本/增加BOSS阶段</t>
-  </si>
-  <si>
-    <t>强化大师</t>
-  </si>
-  <si>
-    <t>强化介绍：为提升强化收益，特推出全身7件强化+7以上赠送强悍属性！&amp;全身7件强化+7：#攻击力/魔法攻击力/诅咒力：3\n防御力：3&amp;全身7件强化+8：#攻击力/魔法攻击力/诅咒力：6\n防御力：6&amp;全身7件强化+9：#攻击力/魔法攻击力/诅咒力：10\n防御力：10&amp;全身7件强化+10：#攻击力/魔法攻击力/诅咒力：15\n防御力：15\n攻击力/魔力/诅咒百分比提升：2.5%\n防具基础防御力提升：5%&amp;全身7件强化+11：#攻击力/魔法攻击力/诅咒力：23\n防御力：23\n攻击力/魔力/诅咒百分比提升：5%\n防具基础防御力提升：10%&amp;全身7件强化+12：#攻击力/魔法攻击力/诅咒力：34\n防御力：34\n攻击力/魔力/诅咒百分比提升：10%\n防具基础防御力提升：18%&amp;全身7件强化+13：#攻击力/魔法攻击力/诅咒力：49\n防御力：49\n攻击力/魔力/诅咒百分比提升：15%\n防具基础防御力提升：28%&amp;全身7件强化+14：#攻击力/魔法攻击力/诅咒力：70\n防御力：70\n攻击力/魔力/诅咒百分比提升：20%\n防具基础防御力提升：40%&amp;全身7件强化+15：#攻击力/魔法攻击力/诅咒力：100\n防御力：100\n攻击力/魔力/诅咒百分比提升：25%\n防具基础防御力提升：55%</t>
+    <t>开启时间#每周一/四/日晚上8点30分&amp;游戏玩法#1.所有拥有战盟的玩家都可进入副本进行战斗。\n2.盟主及副盟主可消耗战盟资金召唤守护者共同战斗。\n3.战斗开始时，会在副本随机刷新出怪物朝狼神护台进攻，玩家需要将怪物在击败狼神护台前进行击杀&amp;狼魂要塞产出：稀有装备，极品套装（非洞装）坐骑材料。&amp;狼魂要塞为行会战盟副本/增加BOSS阶段</t>
   </si>
   <si>
     <t>宝石掉落</t>
@@ -189,13 +194,13 @@
     <t>交易系统</t>
   </si>
   <si>
-    <t>开通畅玩卡：玩家自由交易需双方均畅玩卡。&amp;交易限制：交易双方必须在本服、非副本、同地图内，不超过4格距离，建议选择安全区。&amp;交易税：交易货币存在9%交易税。&amp;交易失败：离线、死亡等异常状况会导致交易失败。 &amp;交易过程中，任何一方关闭界面，交易取消</t>
+    <t>开通畅玩卡：玩家自由使用藏宝阁系统需。&amp;交易税：交易货币存在10%交易税。本服没有自由交易。一切靠打。</t>
   </si>
   <si>
     <t>红名PK系统</t>
   </si>
   <si>
-    <t>PK值：游戏PK线外击杀玩家会增加PK值；击杀非白名玩家不增加PK值。&amp;PK阶段：PK值根据大小对应PK阶段，PK阶段对应不同的死亡惩罚，副本内死亡没有死亡惩罚#白名：一位良民，PVP极小概率掉落宝石道具；死亡掉落4%金币(优先绑金)\n无赖：黄名，PVP有概率掉落宝石道具；死亡掉落4%金币，PVP额外扣除1%金币。\n恶人：红名，PVP较大概率掉落宝石道具；死亡掉落4%金币，PVP额外扣除2%金币；小概率掉落穿戴的装备\n恶魔：红名，PVP死亡极大概率掉落多个宝石道具；死亡掉落4%金币，PVP死亡额外扣除4%金币；PVE小概率掉落穿戴的装备，PVP极大概率掉落穿戴的装备。&amp;其他限制：PK值超过一定值时无法对其他玩家造成伤害，限制交易行使用与和平线路传送&amp;PK值减少：#打怪：玩家可以通过击杀怪物来减少PK值，等级越高减少越多\n免罪符：积分商城内购买，可用于快速清除全部PK点数。&amp;补充：#当掉落的道具为非绑定状态时才可拾取，PVP击杀掉落道具归属与击杀者，PVE无归属。</t>
+    <t>PK值：游戏PK线外击杀玩家会增加PK值；击杀非白名玩家不增加PK值。&amp;PK阶段：PK值根据大小对应PK阶段，PK阶段对应不同的死亡惩罚，副本内死亡没有死亡惩罚#白名：一位良民，PVP极小概率掉落宝石道具；死亡掉落4%金币(优先绑金)\n无赖：黄名，PVP有概率掉落宝石道具；死亡掉落4%金币，PVP额外扣除1%金币。\n恶人：红名，PVP较大概率掉落宝石道具；死亡掉落4%金币，PVP额外扣除2%金币；小概率掉落穿戴的装备\n恶魔：红名，PVP死亡极大概率掉落多个宝石道具；死亡掉落4%金币，PVP死亡额外扣除4%金币；PVE小概率掉落穿戴的装备，PVP极大概率掉落穿戴的装备。&amp;其他限制：PK值超过一定值时无法对其他玩家造成伤害，限制交易行使用与和平线路传送&amp;PK值减少：#打怪：玩家可以通过击杀怪物来减少PK值，等级越高减少越多\n免罪符：积分商城内购买，可用于快速清除全部PK点数。&amp;补充：#掉落的道具直接消失。</t>
   </si>
   <si>
     <t>萤石系统</t>
@@ -207,25 +212,25 @@
     <t>耳环系统</t>
   </si>
   <si>
-    <t>耳环获取详解：#幻术园：23 226 可用灵魂/祝福/玛雅/各一个合成饰品箱子\n可以开出卓越装备/套装/耳环/技能书/耳环/积分/金币/一切看脸。搏一搏单车变摩托。一切皆有可能。 &amp;宝箱系统永远免费合成/全部玩家游戏打材料产出</t>
+    <t xml:space="preserve">耳环获取详解：#仙踪林合成，可用灵魂/祝福/玛雅/各一个合成饰品宝箱\n可以开出卓越装备/套装/耳环/技能书/积分/金币/一切看脸。搏一搏单车变摩托。一切皆有可能。 </t>
   </si>
   <si>
     <t>挂机玩法</t>
   </si>
   <si>
-    <t>挂机点说明：#每条线路/每张大地图/有一个怪物点，。需玩家自行探索&amp;高等级地图会有2-3个</t>
+    <t>挂机点说明：#每张大地图/有几个多怪物点。需玩家自由摸索。</t>
   </si>
   <si>
     <t>合成系统</t>
   </si>
   <si>
-    <t>坐骑合成：#越高等级坐骑出现卓越词条几率越大&amp;满卓越6词条&amp;高等级坐骑增加移动速度&amp;在PVP,PVE中更有优势&amp;翅膀合成：#合成逻辑严格按照1.03H版本支持拔毛\n合成成功率所溢出的材料将会退回到背包不计算在内，保证玩家的材料避免丢失</t>
+    <t>坐骑合成：#越高等级坐骑出现卓越词条几率越大&amp;满卓越6词条&amp;高等级坐骑增加移动速度&amp;在PVP,PVE中更有优势&amp;翅膀合成：#合成逻辑严格按照1.03H版本支持拔毛\n合成成功率所溢出的材料将会退回到背包不计算在内，保证材料避免丢失</t>
   </si>
   <si>
     <t>重要提示</t>
   </si>
   <si>
-    <t>AG/SD详解：#战斗数值复原1.03.Ag值，各职业增加对应的属性点，会有对应的AG/SD值加成。\n具体数值需玩家自行摸索。\nSD值，除基础属性提升，属性加成提升，高等级装备也会增加SD值。&amp;重要货币提醒：所有货币均为单角色储存，同账号多职业/角色不通用。</t>
+    <t>AG/SD详解：#战斗数值复刻国际副.Ag值，各职业增加对应的属性点，会有对应的AG/SD值加成。\n具体数值需玩家自行摸索。\nSD值，除基础属性提升，属性加成提升，高等级装备也会增加SD值。&amp;重要货币提醒：所有货币均为单角色储存，同账号多职业/角色不通用。</t>
   </si>
 </sst>
 </file>
@@ -1611,23 +1616,23 @@
       </c>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" ht="42.75" spans="1:9">
+    <row r="8" ht="28.5" spans="1:9">
       <c r="A8" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="E8" s="3">
         <v>1</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="5">
         <v>1</v>
       </c>
       <c r="G8" s="3">
@@ -1638,12 +1643,12 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" ht="132" customHeight="1" spans="1:9">
+    <row r="9" ht="42.75" spans="1:9">
       <c r="A9" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -1652,10 +1657,10 @@
         <v>48</v>
       </c>
       <c r="E9" s="3">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3">
         <v>9999</v>
@@ -1785,13 +1790,13 @@
       <c r="D14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="3">
         <v>1</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="3">
         <v>1</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="3">
         <v>9999</v>
       </c>
       <c r="H14" s="3" t="s">
@@ -1811,13 +1816,13 @@
       <c r="D15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="3">
         <v>1</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="3">
         <v>1</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="3">
         <v>9999</v>
       </c>
       <c r="H15" s="3" t="s">
@@ -1837,13 +1842,13 @@
       <c r="D16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="3">
         <v>1</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="3">
         <v>1</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="3">
         <v>9999</v>
       </c>
       <c r="H16" s="3" t="s">
@@ -1863,13 +1868,13 @@
       <c r="D17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="3">
         <v>1</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="3">
         <v>1</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="3">
         <v>9999</v>
       </c>
       <c r="H17" s="3" t="s">
